--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>04/08 19:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>10/08 13:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>10/08 23:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>10/08 20:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>07/08 23:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>10/08 18:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>50</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>45</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>02/08 18:30</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/08 17:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>07/08 22:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>55</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>03/08 18:15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>02/08 15:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>55</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>60</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>03/08 22:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>60</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>03/08 23:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>08/08 10:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>60</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>09/08 00:15</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>50</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>60</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>03/08 11:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>50</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>55</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>02/08 19:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F24" t="n">
+        <v>3.6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>03/08 17:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>45</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>05/08 18:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>45</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,142 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45871.07925300718</v>
+        <v>45871.07925300926</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Belgran</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CA Belgrano – CA BanfieldLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>09/08 23:45</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+16,0%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45871.14421302457</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Sport Reci</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sport Recife – Bahia Salvador BABrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>02/08 19:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>39,1%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+7,62%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45871.14421302457</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | Gaziantep </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Gaziantep FK – GalatasaraySüper Lig</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>08/08 18:30</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+5,97%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45871.14421302457</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -1580,10 +1580,8 @@
           <t>09/08 23:45</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>50</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45871.14421302457</v>
+        <v>45871.14421302083</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>02/08 19:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.75</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45871.14421302457</v>
+        <v>45871.14421302083</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>08/08 18:30</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>50</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45871.14421302457</v>
+        <v>45871.14421302083</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1683,6 +1683,51 @@
         <v>45871.14421302083</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CFR Cluj –</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CFR Cluj – Sporting BragaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>07/08 17:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+46,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45871.22671788447</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>07/08 17:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>50</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,142 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45871.22671788447</v>
+        <v>45871.22671788195</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Atletico M</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>39,8%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+39,2%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45871.2728193868</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vitoria BA – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>03/08 22:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45871.2728193868</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Ceara CE –</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ceara CE – FlamengoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+20,1%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45871.2728193868</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45871.2728193868</v>
+        <v>45871.27281938658</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>03/08 22:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F32" t="n">
+        <v>3.1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45871.2728193868</v>
+        <v>45871.27281938658</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F33" t="n">
+        <v>3.5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45871.2728193868</v>
+        <v>45871.27281938658</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs1re équipe | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mirassol – Vasco de GamaBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>02/08 21:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+22,8%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45871.30669472585</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Plus que 2.51re période1re équipe | Deportes I</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Deportes Iquique – Universidad CatolicaChili - Primera Division</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re période1re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>02/08 21:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+17,1%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45871.30669472585</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F34" t="n">
+        <v>3.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45871.30669472585</v>
+        <v>45871.30669472223</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>50</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,142 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45871.30669472585</v>
+        <v>45871.30669472223</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FCSB – KF </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>FCSB – KF DritaLigue Europa stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>07/08 18:30</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+57,4%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45871.35337477109</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs2e équipe | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mirassol – Vasco de GamaBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>02/08 21:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+18,4%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45871.35337477109</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Fluminense</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fluminense – Gremio RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>03/08 00:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>36,1%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+15,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45871.35337477109</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>07/08 18:30</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>55</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45871.35337477109</v>
+        <v>45871.35337476852</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.7</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45871.35337477109</v>
+        <v>45871.35337476852</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F38" t="n">
+        <v>3.2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,97 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45871.35337477109</v>
+        <v>45871.35337476852</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | Fluminense</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fluminense – Gremio RSBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>03/08 00:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>43,4%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+19,4%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45871.39293636099</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Alex Miche</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Alex Michelsen – Learner TienATP - Toronto</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02/08 16:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>81,9%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45871.39293636099</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -2096,10 +2096,8 @@
           <t>03/08 00:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.75</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45871.39293636099</v>
+        <v>45871.39293636574</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>02/08 16:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
+      <c r="F40" t="n">
+        <v>1.4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45871.39293636099</v>
+        <v>45871.39293636574</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,6 +2156,51 @@
         <v>45871.39293636574</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Defensa y </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia – Deportivo RiestraLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>11/08 22:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+46,3%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45871.47213623062</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,23 +2182,66 @@
           <t>11/08 22:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>60</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+46,3%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45871.47213622685</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Independie</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Independiente Medellin – Millonarios FCPrimera A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>03/08 23:20</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>+46,3%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>45871.47213623062</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+50,2%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45871.53125276257</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>03/08 23:20</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>60</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,52 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45871.53125276257</v>
+        <v>45871.5312527662</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 29.5 - tirs | Atletico M</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Atletico Mineiro – BragantinoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 29.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>03/08 21:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45871.5641372255</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -2268,10 +2268,8 @@
           <t>03/08 21:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.9</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45871.5641372255</v>
+        <v>45871.56413722222</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2285,6 +2285,96 @@
         <v>45871.56413722222</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Tecnico Un</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tecnico Universitario – Manta FCSerie A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>03/08 20:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+9,19%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45871.64111716785</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 15.5 - tirs1re équipe | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lech Poznan – Gornik ZabrzePologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 15.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>02/08 18:15</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>50,6%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+8,77%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45871.64111716785</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -2311,10 +2311,8 @@
           <t>03/08 20:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>40</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45871.64111716785</v>
+        <v>45871.64111716435</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2354,8 @@
           <t>02/08 18:15</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F45" t="n">
+        <v>2.15</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2372,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45871.64111716785</v>
+        <v>45871.64111716435</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2371,6 +2371,51 @@
         <v>45871.64111716435</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | TSC Backa </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TSC Backa Topola – Spartak SuboticaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02/08 18:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+8,52%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45871.72228435023</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,23 +2397,201 @@
           <t>02/08 18:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>40</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+8,52%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45871.72228435185</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Dainava Al</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Dainava Alytus – FK SuduvaA Lyga</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>03/08 15:25</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>+8,52%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>45871.72228435023</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+14,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45871.77235655922</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Swansea – </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Swansea – Crawley TownEFL Cup</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>12/08 18:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+9,19%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45871.77235655922</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PMU(FR)Football | 1(0:1) | BK Häcken </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BK Häcken – BrannEurope. Europa League (Q)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1(0:1)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>07/08 17:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>18,9%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+5,81%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45871.77235655922</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Trabzonspo</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Trabzonspor – KocaelisporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>11/08 18:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+4,65%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45871.77235655922</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>03/08 15:25</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>40</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45871.77235655922</v>
+        <v>45871.7723565625</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>12/08 18:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>55</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45871.77235655922</v>
+        <v>45871.7723565625</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>07/08 17:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>5.60</t>
-        </is>
+      <c r="F49" t="n">
+        <v>5.6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45871.77235655922</v>
+        <v>45871.7723565625</v>
       </c>
     </row>
     <row r="50">
@@ -2575,10 +2569,8 @@
           <t>11/08 18:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>45</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2591,7 +2583,97 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45871.77235655922</v>
+        <v>45871.7723565625</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Fenerbahce</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Fenerbahce – AlanyasporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>09/08 18:30</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+12,6%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45871.80445374468</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | C.Tauson –</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C.Tauson – I.SwiatekWTA - Montreal F</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>03/08 16:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>47,8%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+2,85%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45871.80445374468</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>09/08 18:30</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>50</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45871.80445374468</v>
+        <v>45871.80445375</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>03/08 16:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.15</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,97 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45871.80445374468</v>
+        <v>45871.80445375</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Nacional A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Nacional Asuncion – CS 2 de MayoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02/08 21:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+34,3%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45871.8506098181</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Rionegro A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Rionegro Aguilas – Fortaleza FCPrimera A - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>04/08 01:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+4,37%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45871.8506098181</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2698,10 +2698,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>50</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2714,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45871.8506098181</v>
+        <v>45871.85060981481</v>
       </c>
     </row>
     <row r="54">
@@ -2743,10 +2741,8 @@
           <t>04/08 01:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>40</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2759,7 +2755,97 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45871.8506098181</v>
+        <v>45871.85060981481</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Barcelona </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Barcelona SC – Orense SCSerie A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>02/08 21:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+15,4%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45871.88985939282</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | EC Bahia –</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EC Bahia – FluminenseSérie A</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>10/08 00:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+4,99%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45871.88985939282</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>02/08 21:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>45</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45871.88985939282</v>
+        <v>45871.88985939815</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>10/08 00:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>45</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,52 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45871.88985939282</v>
+        <v>45871.88985939815</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Deportivo </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira – Once CaldasPrimera A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>03/08 19:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+2,11%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45871.93238641308</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-02.xlsx
+++ b/data/valuebets_database_2025-08-02.xlsx
@@ -2870,10 +2870,8 @@
           <t>03/08 19:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>40</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45871.93238641308</v>
+        <v>45871.93238641204</v>
       </c>
     </row>
   </sheetData>
